--- a/University_journal/University_journal.xlsx
+++ b/University_journal/University_journal.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\din20\OneDrive\Документы\GitHub\java-io-DINNIESHAY\University_journal\"/>
     </mc:Choice>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="46">
   <si>
     <t>ID</t>
   </si>
@@ -182,11 +182,21 @@
 Абдурахманов Анвар Шавкатович
 ауд. 1306</t>
   </si>
+  <si>
+    <t>Гафаров Тимур Бахтиярович</t>
+  </si>
+  <si>
+    <t>Ильина Екатерина Анатольевна</t>
+  </si>
+  <si>
+    <t>Попович Динара Ильназовна</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -545,13 +555,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="26.77734375" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="3" width="10.109375"/>
+    <col min="2" max="2" customWidth="true" width="26.77734375"/>
+    <col min="3" max="3" customWidth="true" style="3" width="11.33203125"/>
+    <col min="4" max="4" customWidth="true" width="20.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -572,13 +582,13 @@
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>18</v>
       </c>
     </row>
@@ -586,13 +596,13 @@
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>19</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>23</v>
       </c>
     </row>
@@ -600,13 +610,13 @@
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>21</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>22</v>
       </c>
     </row>
@@ -614,13 +624,41 @@
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C7" t="n" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
         <v>18</v>
       </c>
     </row>
@@ -644,42 +682,42 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="0">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>20</v>
       </c>
     </row>
@@ -694,11 +732,11 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="34.21875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" customWidth="true" style="3" width="10.77734375"/>
+    <col min="2" max="2" customWidth="true" style="5" width="34.21875"/>
+    <col min="3" max="3" customWidth="true" style="3" width="12.77734375"/>
+    <col min="4" max="4" customWidth="true" style="3" width="20.5546875"/>
+    <col min="5" max="16384" style="3" width="8.88671875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -781,10 +819,10 @@
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="3"/>
-    <col min="3" max="3" width="11.88671875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="2" style="3" width="8.88671875"/>
+    <col min="3" max="3" customWidth="true" style="3" width="11.88671875"/>
+    <col min="4" max="4" customWidth="true" style="3" width="11.77734375"/>
+    <col min="5" max="16384" style="3" width="8.88671875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1218,9 +1256,9 @@
   <dimension ref="A1:AX43"/>
   <sheetFormatPr defaultColWidth="36.77734375" defaultRowHeight="51.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
-    <col min="2" max="6" width="36.77734375" style="6"/>
-    <col min="7" max="50" width="36.77734375" style="3"/>
+    <col min="1" max="1" customWidth="true" width="18.44140625"/>
+    <col min="2" max="6" style="6" width="36.77734375"/>
+    <col min="7" max="50" style="3" width="36.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="2" customFormat="1" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1288,7 +1326,7 @@
       <c r="AX1" s="1"/>
     </row>
     <row r="2" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -1296,7 +1334,7 @@
       </c>
     </row>
     <row r="3" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>11</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -1305,7 +1343,7 @@
       <c r="C3" s="7"/>
     </row>
     <row r="4" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
@@ -1316,7 +1354,7 @@
       </c>
     </row>
     <row r="5" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>13</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -1324,7 +1362,7 @@
       </c>
     </row>
     <row r="6" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>14</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -1332,17 +1370,17 @@
       </c>
     </row>
     <row r="7" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>10</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -1350,7 +1388,7 @@
       </c>
     </row>
     <row r="10" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>11</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -1361,7 +1399,7 @@
       </c>
     </row>
     <row r="11" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -1372,7 +1410,7 @@
       </c>
     </row>
     <row r="12" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="0">
         <v>13</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -1380,22 +1418,22 @@
       </c>
     </row>
     <row r="13" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" t="s" s="0">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" t="s" s="0">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" t="s" s="0">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:50" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B16" s="7" t="s">
@@ -1404,7 +1442,7 @@
       <c r="C16" s="7"/>
     </row>
     <row r="17" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" t="s" s="0">
         <v>11</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -1415,7 +1453,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" t="s" s="0">
         <v>12</v>
       </c>
       <c r="B18" s="7" t="s">
@@ -1426,7 +1464,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" t="s" s="0">
         <v>13</v>
       </c>
       <c r="B19" s="7"/>
@@ -1435,27 +1473,27 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" t="s" s="0">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" t="s" s="0">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" t="s" s="0">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" t="s" s="0">
         <v>11</v>
       </c>
       <c r="B24" s="7" t="s">
@@ -1463,7 +1501,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" t="s" s="0">
         <v>12</v>
       </c>
       <c r="B25" s="7" t="s">
@@ -1474,7 +1512,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" t="s" s="0">
         <v>13</v>
       </c>
       <c r="B26" s="7" t="s">
@@ -1485,7 +1523,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B27" s="7"/>
@@ -1494,91 +1532,91 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" t="s" s="0">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" t="s" s="0">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B30" s="7"/>
     </row>
     <row r="31" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" t="s" s="0">
         <v>11</v>
       </c>
       <c r="B31" s="7"/>
     </row>
     <row r="32" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" t="s" s="0">
         <v>12</v>
       </c>
       <c r="B32" s="7"/>
     </row>
     <row r="33" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" t="s" s="0">
         <v>13</v>
       </c>
       <c r="C33" s="7"/>
     </row>
     <row r="34" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" t="s" s="0">
         <v>14</v>
       </c>
       <c r="C34" s="7"/>
     </row>
     <row r="35" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" t="s" s="0">
         <v>15</v>
       </c>
       <c r="C35" s="7"/>
     </row>
     <row r="36" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" t="s" s="0">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" t="s" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" t="s" s="0">
         <v>12</v>
       </c>
       <c r="B39" s="7"/>
     </row>
     <row r="40" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" t="s" s="0">
         <v>13</v>
       </c>
       <c r="B40" s="7"/>
     </row>
     <row r="41" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B41" s="7"/>
     </row>
     <row r="42" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" t="s" s="0">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" t="s" s="0">
         <v>16</v>
       </c>
     </row>
@@ -1593,8 +1631,8 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="38.6640625" style="5" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="3" width="8.109375"/>
+    <col min="2" max="2" customWidth="true" style="5" width="38.6640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">

--- a/University_journal/University_journal.xlsx
+++ b/University_journal/University_journal.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="53">
   <si>
     <t>ID</t>
   </si>
@@ -190,6 +190,27 @@
   </si>
   <si>
     <t>Попович Динара Ильназовна</t>
+  </si>
+  <si>
+    <t>Бабушкина Елизавета Петровна</t>
+  </si>
+  <si>
+    <t>Шаинов Леонид Владимирович</t>
+  </si>
+  <si>
+    <t>Балонина Ангелина Алексеевна</t>
+  </si>
+  <si>
+    <t>Иванов Иван Иванович</t>
+  </si>
+  <si>
+    <t>11-406</t>
+  </si>
+  <si>
+    <t>Философия</t>
+  </si>
+  <si>
+    <t>Лагутин Марк Владимирович</t>
   </si>
 </sst>
 </file>
@@ -555,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="3" width="10.109375"/>
@@ -662,6 +683,62 @@
         <v>18</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C8" t="n" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C9" t="n" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C10" t="n" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C11" t="n" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -670,7 +747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -719,6 +796,14 @@
       </c>
       <c r="B6" t="s" s="0">
         <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -729,7 +814,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="3" width="10.77734375"/>
@@ -809,6 +894,20 @@
         <v>30</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="5">
+        <v>52</v>
+      </c>
+      <c r="C6" t="n" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="3">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -816,7 +915,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" style="3" width="8.88671875"/>
@@ -1243,6 +1342,62 @@
       </c>
       <c r="D30" s="3">
         <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="B31" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C31" t="n" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D31" t="n" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n" s="3">
+        <v>31.0</v>
+      </c>
+      <c r="B32" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C32" t="n" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D32" t="n" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n" s="3">
+        <v>32.0</v>
+      </c>
+      <c r="B33" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C33" t="n" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D33" t="n" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n" s="3">
+        <v>33.0</v>
+      </c>
+      <c r="B34" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C34" t="n" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D34" t="n" s="3">
+        <v>6.0</v>
       </c>
     </row>
   </sheetData>
@@ -1628,7 +1783,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="3" width="8.109375"/>
@@ -1675,6 +1830,14 @@
         <v>28</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="5">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
